--- a/app/dist/Archivos/Template/Template_HRC_farmatodo.xlsx
+++ b/app/dist/Archivos/Template/Template_HRC_farmatodo.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9/16/25</t>
+          <t>10/6/25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
